--- a/assets/report_template.xlsx
+++ b/assets/report_template.xlsx
@@ -8,7 +8,7 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原始个体与质量" sheetId="4" r:id="Rd22b70cb35b24c10"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="鱼对关系" sheetId="5" r:id="R51b0413c9e974c24"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数与方法" sheetId="6" r:id="R93a1e75c87ce4d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考文献" sheetId="7" r:id="R8cdc4e94a1804c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="7" r:id="R8cdc4e94a1804c1e"/>
   </x:sheets>
 </x:workbook>
 </file>
